--- a/zbm_summary.xlsx
+++ b/zbm_summary.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAWARUX1\email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A81F3E73-4E2D-4410-93C0-3E94F9D1C792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B723A0C9-B761-489D-BB27-C1FB5B728B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0E96A2CA-FF2B-4A2D-B270-07BA2EE2A305}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{0E96A2CA-FF2B-4A2D-B270-07BA2EE2A305}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Division" sheetId="4" r:id="rId1"/>
+    <sheet name="ZBM" sheetId="1" r:id="rId2"/>
+    <sheet name="ABM" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,52 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t># ABMs ID</t>
-  </si>
-  <si>
-    <t># ABMs Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Unique HCPs Participating </t>
-  </si>
-  <si>
-    <t># Requests Raised</t>
-  </si>
-  <si>
-    <t>Action pending / In Process At HO</t>
-  </si>
-  <si>
-    <t>Action pending / In Process At HUB</t>
-  </si>
-  <si>
-    <t># Requests Dispatched</t>
-  </si>
-  <si>
-    <t>Delivered</t>
-  </si>
-  <si>
-    <t>Dispatched &amp; In Transit</t>
-  </si>
-  <si>
-    <t>Lost &amp; In Transit</t>
-  </si>
-  <si>
-    <t>RTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Incomplete Address</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Dr. Non contactable</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Doctor refused to accept</t>
-  </si>
-  <si>
-    <t>-RTO due to hold delivery</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="60">
   <si>
     <t>Munish Kalra</t>
   </si>
@@ -93,13 +50,184 @@
   </si>
   <si>
     <t>ATAUR RAHAMAN</t>
+  </si>
+  <si>
+    <t>HO</t>
+  </si>
+  <si>
+    <t>HUB</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>IA0001 - Ahmedabad</t>
+  </si>
+  <si>
+    <t>IA0002 - Mumbai</t>
+  </si>
+  <si>
+    <t>IA0003 - Pune</t>
+  </si>
+  <si>
+    <t>IA0004 - Nagpur</t>
+  </si>
+  <si>
+    <t>Delivery Status</t>
+  </si>
+  <si>
+    <t>RTO Reasons</t>
+  </si>
+  <si>
+    <t>Request Cancelled / Out of Stock (A)</t>
+  </si>
+  <si>
+    <t>Action pending / In Process At HO (B)</t>
+  </si>
+  <si>
+    <t># Requests Raised
+(A+B+C)</t>
+  </si>
+  <si>
+    <t>Pending for Invoicing (D)</t>
+  </si>
+  <si>
+    <t>Pending for Dispatch (E)</t>
+  </si>
+  <si>
+    <t>Sent to HUB ('C)
+(D+E+F)</t>
+  </si>
+  <si>
+    <t>Delivered (G)</t>
+  </si>
+  <si>
+    <t>Dispatched &amp; In Transit (H)</t>
+  </si>
+  <si>
+    <t>RTO (I)</t>
+  </si>
+  <si>
+    <t># Requests Dispatched (F)
+(G+H+I)</t>
+  </si>
+  <si>
+    <t>Incomplete Address</t>
+  </si>
+  <si>
+    <t>Doctor Non Contactable</t>
+  </si>
+  <si>
+    <t>Doctor Refused to Accept</t>
+  </si>
+  <si>
+    <t>Hold Delivery</t>
+  </si>
+  <si>
+    <t>ABM Name</t>
+  </si>
+  <si>
+    <t>Area Name</t>
+  </si>
+  <si>
+    <t>HQ</t>
+  </si>
+  <si>
+    <t>TBM Name</t>
+  </si>
+  <si>
+    <t>IT0001 - Ahmedabad</t>
+  </si>
+  <si>
+    <t>IT0002 - Mumbai</t>
+  </si>
+  <si>
+    <t>IT0003 - Pune</t>
+  </si>
+  <si>
+    <t>IT0004 - Nagpur</t>
+  </si>
+  <si>
+    <t>Zone Name</t>
+  </si>
+  <si>
+    <t>ZBM Name</t>
+  </si>
+  <si>
+    <t>ZN0001 - Ahmedabad</t>
+  </si>
+  <si>
+    <t>ZN0002 - Mumbai</t>
+  </si>
+  <si>
+    <t>ZN0003 - Pune</t>
+  </si>
+  <si>
+    <t>ZN0004 - Nagpur</t>
+  </si>
+  <si>
+    <t># Unique HCPs</t>
+  </si>
+  <si>
+    <t># Unique TBMs</t>
+  </si>
+  <si>
+    <t>YTD</t>
+  </si>
+  <si>
+    <t>Doctor: Customer Code</t>
+  </si>
+  <si>
+    <t>Assigned Request Ids</t>
+  </si>
+  <si>
+    <t>Input Sample Request: Created By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request Status - Out of Stock </t>
+  </si>
+  <si>
+    <t>Action pending / In Process, Dispatch &amp; in Transit, Dispatch Pending</t>
+  </si>
+  <si>
+    <t>ABM Terr Code</t>
+  </si>
+  <si>
+    <t>unique count of (Doctor: Customer Code)</t>
+  </si>
+  <si>
+    <t>unique count of (Assigned Request Ids)</t>
+  </si>
+  <si>
+    <t>unique count of (Request Status)-Request Raised</t>
+  </si>
+  <si>
+    <t>unique count of (Request Status)-Out Of  Stock + On hold+nor permited</t>
+  </si>
+  <si>
+    <t>unique count of (Request Status)-Delivered, Return, Action pending / In Process, Dispatched &amp; In Transit, Dispatch Pending</t>
+  </si>
+  <si>
+    <t>unique count of (Request Status)-Action Pending / in Process</t>
+  </si>
+  <si>
+    <t>unique count of (Request Status)-Dispatch Pending</t>
+  </si>
+  <si>
+    <t>unique count of (Request Status)-Dispatched &amp; In Transit</t>
+  </si>
+  <si>
+    <t>unique count of (Request Status)-Delivered</t>
+  </si>
+  <si>
+    <t>unique count of (Request Status)-RTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,39 +237,95 @@
     </font>
     <font>
       <b/>
-      <sz val="5"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="5"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="5"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="5"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="5"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF56585B"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -162,24 +346,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0E6F5"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD0D0D0"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -188,26 +390,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -219,21 +438,132 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="medium">
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -243,34 +573,189 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -605,246 +1090,1218 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9760C12-457D-4B77-BE71-2AFD5C035BB8}">
+  <dimension ref="B1:T8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="11.1796875" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" style="2" customWidth="1"/>
+    <col min="15" max="19" width="11.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1"/>
+    </row>
+    <row r="2" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="56"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="39"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="42"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="2:20" ht="52" x14ac:dyDescent="0.35">
+      <c r="B3" s="48"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B4" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="18">
+        <v>12</v>
+      </c>
+      <c r="F4" s="22">
+        <v>13</v>
+      </c>
+      <c r="G4" s="26">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="27">
+        <f>F4-G4-H4</f>
+        <v>12</v>
+      </c>
+      <c r="J4" s="26">
+        <v>2</v>
+      </c>
+      <c r="K4" s="4">
+        <v>1</v>
+      </c>
+      <c r="L4" s="18">
+        <v>10</v>
+      </c>
+      <c r="M4" s="26">
+        <v>9</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1</v>
+      </c>
+      <c r="O4" s="18">
+        <v>0</v>
+      </c>
+      <c r="P4" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="18">
+        <v>13</v>
+      </c>
+      <c r="F5" s="22">
+        <v>15</v>
+      </c>
+      <c r="G5" s="26"/>
+      <c r="H5" s="4">
+        <v>2</v>
+      </c>
+      <c r="I5" s="27"/>
+      <c r="J5" s="26">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="18">
+        <v>13</v>
+      </c>
+      <c r="M5" s="26">
+        <v>11</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1</v>
+      </c>
+      <c r="O5" s="18">
+        <v>1</v>
+      </c>
+      <c r="P5" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
+      <c r="S5" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B6" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="18">
+        <v>76</v>
+      </c>
+      <c r="F6" s="22">
+        <v>80</v>
+      </c>
+      <c r="G6" s="26"/>
+      <c r="H6" s="4">
+        <v>3</v>
+      </c>
+      <c r="I6" s="27"/>
+      <c r="J6" s="26">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="18">
+        <v>77</v>
+      </c>
+      <c r="M6" s="26">
+        <v>77</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="18">
+        <v>0</v>
+      </c>
+      <c r="P6" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B7" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="18">
+        <v>12</v>
+      </c>
+      <c r="F7" s="22">
+        <v>25</v>
+      </c>
+      <c r="G7" s="26"/>
+      <c r="H7" s="4">
+        <v>4</v>
+      </c>
+      <c r="I7" s="27"/>
+      <c r="J7" s="26">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="18">
+        <v>21</v>
+      </c>
+      <c r="M7" s="26">
+        <v>13</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="18">
+        <v>8</v>
+      </c>
+      <c r="P7" s="26">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>2</v>
+      </c>
+      <c r="S7" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="19"/>
+      <c r="C8" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="21">
+        <f>SUM(E4:E7)</f>
+        <v>113</v>
+      </c>
+      <c r="F8" s="23">
+        <f t="shared" ref="F8:S8" si="0">SUM(F4:F7)</f>
+        <v>133</v>
+      </c>
+      <c r="G8" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="29">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I8" s="21">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="J8" s="28">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K8" s="29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L8" s="21">
+        <f t="shared" si="0"/>
+        <v>121</v>
+      </c>
+      <c r="M8" s="28">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="N8" s="29">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O8" s="21">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="P8" s="28">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Q8" s="29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R8" s="29">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="S8" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DACB1CB7-14A2-4E13-A57E-9A753E37F862}">
-  <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:S9"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.81640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="17" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="10"/>
+    <col min="5" max="5" width="12.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.90625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" style="10" customWidth="1"/>
+    <col min="8" max="13" width="13.90625" style="10" customWidth="1"/>
+    <col min="14" max="14" width="13.90625" style="14" customWidth="1"/>
+    <col min="15" max="19" width="13.90625" style="10" customWidth="1"/>
+    <col min="20" max="16384" width="8.7265625" style="10"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="2:19" ht="186" x14ac:dyDescent="0.35">
+      <c r="B1" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="O1" s="36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="2:19" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="C2" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="10"/>
+    </row>
+    <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="61" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="62" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+    </row>
+    <row r="4" spans="2:19" ht="39" x14ac:dyDescent="0.3">
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12">
+        <v>12</v>
+      </c>
+      <c r="F5" s="12">
+        <v>13</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0</v>
+      </c>
+      <c r="H5" s="12">
+        <v>1</v>
+      </c>
+      <c r="I5" s="15">
+        <f>F5-G5-H5</f>
+        <v>12</v>
+      </c>
+      <c r="J5" s="12">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="K5" s="12">
+        <v>1</v>
+      </c>
+      <c r="L5" s="12">
+        <v>10</v>
+      </c>
+      <c r="M5" s="12">
+        <v>9</v>
+      </c>
+      <c r="N5" s="12">
+        <v>1</v>
+      </c>
+      <c r="O5" s="12">
+        <v>0</v>
+      </c>
+      <c r="P5" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>0</v>
+      </c>
+      <c r="R5" s="12">
+        <v>0</v>
+      </c>
+      <c r="S5" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="12">
+        <v>13</v>
+      </c>
+      <c r="F6" s="12">
+        <v>15</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12">
+        <v>2</v>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="12">
+        <v>0</v>
+      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12">
+        <v>13</v>
+      </c>
+      <c r="M6" s="12">
+        <v>11</v>
+      </c>
+      <c r="N6" s="12">
+        <v>1</v>
+      </c>
+      <c r="O6" s="12">
+        <v>1</v>
+      </c>
+      <c r="P6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>1</v>
+      </c>
+      <c r="R6" s="12">
+        <v>0</v>
+      </c>
+      <c r="S6" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="12">
+        <v>76</v>
+      </c>
+      <c r="F7" s="12">
+        <v>80</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="I7" s="15"/>
+      <c r="J7" s="12">
+        <v>0</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12">
+        <v>77</v>
+      </c>
+      <c r="M7" s="12">
+        <v>77</v>
+      </c>
+      <c r="N7" s="12">
+        <v>0</v>
+      </c>
+      <c r="O7" s="12">
+        <v>0</v>
+      </c>
+      <c r="P7" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>0</v>
+      </c>
+      <c r="R7" s="12">
+        <v>0</v>
+      </c>
+      <c r="S7" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="12">
+        <v>12</v>
+      </c>
+      <c r="F8" s="12">
+        <v>25</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="I8" s="15"/>
+      <c r="J8" s="12">
+        <v>0</v>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12">
+        <v>21</v>
+      </c>
+      <c r="M8" s="12">
+        <v>13</v>
+      </c>
+      <c r="N8" s="12">
+        <v>0</v>
+      </c>
+      <c r="O8" s="12">
+        <v>8</v>
+      </c>
+      <c r="P8" s="12">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>2</v>
+      </c>
+      <c r="S8" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="16">
+        <f>SUM(E5:E8)</f>
+        <v>113</v>
+      </c>
+      <c r="F9" s="16">
+        <f t="shared" ref="F9:S9" si="0">SUM(F5:F8)</f>
+        <v>133</v>
+      </c>
+      <c r="G9" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="16">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I9" s="16">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="J9" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K9" s="16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L9" s="16">
+        <f t="shared" si="0"/>
+        <v>121</v>
+      </c>
+      <c r="M9" s="16">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="N9" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O9" s="16">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="P9" s="16">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Q9" s="16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R9" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="S9" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D3:D4"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5345E43-6F29-4205-A85E-B8E01B76C185}">
+  <dimension ref="B1:S8"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.81640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.7265625" style="10"/>
+    <col min="6" max="13" width="12.90625" style="10" customWidth="1"/>
+    <col min="14" max="14" width="12.90625" style="14" customWidth="1"/>
+    <col min="15" max="19" width="12.90625" style="10" customWidth="1"/>
+    <col min="20" max="16384" width="8.7265625" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="N1" s="10"/>
+    </row>
+    <row r="2" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="62" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+    </row>
+    <row r="3" spans="2:19" ht="39" x14ac:dyDescent="0.3">
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="12">
+        <v>12</v>
+      </c>
+      <c r="F4" s="12">
+        <v>13</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12">
+        <v>1</v>
+      </c>
+      <c r="I4" s="15">
+        <f>F4-G4-H4</f>
+        <v>12</v>
+      </c>
+      <c r="J4" s="12">
+        <v>2</v>
+      </c>
+      <c r="K4" s="12">
+        <v>1</v>
+      </c>
+      <c r="L4" s="12">
+        <v>10</v>
+      </c>
+      <c r="M4" s="12">
+        <v>9</v>
+      </c>
+      <c r="N4" s="12">
+        <v>1</v>
+      </c>
+      <c r="O4" s="12">
+        <v>0</v>
+      </c>
+      <c r="P4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <v>0</v>
+      </c>
+      <c r="S4" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12">
+        <v>13</v>
+      </c>
+      <c r="F5" s="12">
+        <v>15</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12">
+        <v>2</v>
+      </c>
+      <c r="I5" s="15"/>
+      <c r="J5" s="12">
+        <v>0</v>
+      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12">
+        <v>13</v>
+      </c>
+      <c r="M5" s="12">
+        <v>11</v>
+      </c>
+      <c r="N5" s="12">
+        <v>1</v>
+      </c>
+      <c r="O5" s="12">
+        <v>1</v>
+      </c>
+      <c r="P5" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>1</v>
+      </c>
+      <c r="R5" s="12">
+        <v>0</v>
+      </c>
+      <c r="S5" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="12">
+        <v>76</v>
+      </c>
+      <c r="F6" s="12">
+        <v>80</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12">
+        <v>3</v>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="12">
+        <v>0</v>
+      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12">
+        <v>77</v>
+      </c>
+      <c r="M6" s="12">
+        <v>77</v>
+      </c>
+      <c r="N6" s="12">
+        <v>0</v>
+      </c>
+      <c r="O6" s="12">
+        <v>0</v>
+      </c>
+      <c r="P6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>0</v>
+      </c>
+      <c r="R6" s="12">
+        <v>0</v>
+      </c>
+      <c r="S6" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="12">
+        <v>12</v>
+      </c>
+      <c r="F7" s="12">
+        <v>25</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12">
+        <v>4</v>
+      </c>
+      <c r="I7" s="15"/>
+      <c r="J7" s="12">
+        <v>0</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12">
+        <v>21</v>
+      </c>
+      <c r="M7" s="12">
+        <v>13</v>
+      </c>
+      <c r="N7" s="12">
+        <v>0</v>
+      </c>
+      <c r="O7" s="12">
+        <v>8</v>
+      </c>
+      <c r="P7" s="12">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="Q7" s="12">
+        <v>0</v>
+      </c>
+      <c r="R7" s="12">
+        <v>2</v>
+      </c>
+      <c r="S7" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="16">
+        <f>SUM(E4:E7)</f>
+        <v>113</v>
+      </c>
+      <c r="F8" s="16">
+        <f t="shared" ref="F8:S8" si="0">SUM(F4:F7)</f>
+        <v>133</v>
+      </c>
+      <c r="G8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="16">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I8" s="16">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="J8" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K8" s="16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L8" s="16">
+        <f t="shared" si="0"/>
+        <v>121</v>
+      </c>
+      <c r="M8" s="16">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="N8" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O8" s="16">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6">
-        <v>730664</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="8">
-        <v>12</v>
-      </c>
-      <c r="D2" s="8">
-        <v>13</v>
-      </c>
-      <c r="E2" s="8">
-        <v>1</v>
-      </c>
-      <c r="F2" s="8">
+      <c r="P8" s="16">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Q8" s="16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R8" s="16">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G2" s="9">
-        <v>10</v>
-      </c>
-      <c r="H2" s="8">
-        <v>9</v>
-      </c>
-      <c r="I2" s="8">
-        <v>1</v>
-      </c>
-      <c r="J2" s="8">
-        <v>0</v>
-      </c>
-      <c r="K2" s="8">
-        <v>0</v>
-      </c>
-      <c r="L2" s="8">
-        <v>0</v>
-      </c>
-      <c r="M2" s="8">
-        <v>0</v>
-      </c>
-      <c r="N2" s="8">
-        <v>0</v>
-      </c>
-      <c r="O2" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6">
-        <v>303361</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="8">
-        <v>13</v>
-      </c>
-      <c r="D3" s="8">
-        <v>15</v>
-      </c>
-      <c r="E3" s="8">
-        <v>2</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0</v>
-      </c>
-      <c r="G3" s="9">
-        <v>13</v>
-      </c>
-      <c r="H3" s="8">
-        <v>11</v>
-      </c>
-      <c r="I3" s="8">
-        <v>1</v>
-      </c>
-      <c r="J3" s="8">
-        <v>0</v>
-      </c>
-      <c r="K3" s="8">
-        <v>1</v>
-      </c>
-      <c r="L3" s="8">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8">
-        <v>1</v>
-      </c>
-      <c r="N3" s="8">
-        <v>0</v>
-      </c>
-      <c r="O3" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="6">
-        <v>725832</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="8">
-        <v>76</v>
-      </c>
-      <c r="D4" s="8">
-        <v>80</v>
-      </c>
-      <c r="E4" s="8">
-        <v>3</v>
-      </c>
-      <c r="F4" s="8">
-        <v>0</v>
-      </c>
-      <c r="G4" s="9">
-        <v>77</v>
-      </c>
-      <c r="H4" s="8">
-        <v>77</v>
-      </c>
-      <c r="I4" s="8">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="6">
-        <v>29613</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="8">
-        <v>12</v>
-      </c>
-      <c r="D5" s="8">
-        <v>25</v>
-      </c>
-      <c r="E5" s="8">
-        <v>4</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9">
-        <v>21</v>
-      </c>
-      <c r="H5" s="8">
-        <v>13</v>
-      </c>
-      <c r="I5" s="8">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8">
-        <v>8</v>
-      </c>
-      <c r="L5" s="8">
-        <v>6</v>
-      </c>
-      <c r="M5" s="8">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8">
-        <v>2</v>
-      </c>
-      <c r="O5" s="8">
+      <c r="S8" s="16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:I2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/zbm_summary.xlsx
+++ b/zbm_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAWARUX1\email\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\email automation\email-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B723A0C9-B761-489D-BB27-C1FB5B728B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7642503-97CB-4DB0-96E5-850578461BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{0E96A2CA-FF2B-4A2D-B270-07BA2EE2A305}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{0E96A2CA-FF2B-4A2D-B270-07BA2EE2A305}"/>
   </bookViews>
   <sheets>
     <sheet name="Division" sheetId="4" r:id="rId1"/>
@@ -29,16 +29,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="57">
   <si>
     <t>Munish Kalra</t>
   </si>
@@ -178,21 +179,9 @@
     <t>Doctor: Customer Code</t>
   </si>
   <si>
-    <t>Assigned Request Ids</t>
-  </si>
-  <si>
     <t>Input Sample Request: Created By</t>
   </si>
   <si>
-    <t xml:space="preserve">Request Status - Out of Stock </t>
-  </si>
-  <si>
-    <t>Action pending / In Process, Dispatch &amp; in Transit, Dispatch Pending</t>
-  </si>
-  <si>
-    <t>ABM Terr Code</t>
-  </si>
-  <si>
     <t>unique count of (Doctor: Customer Code)</t>
   </si>
   <si>
@@ -221,13 +210,16 @@
   </si>
   <si>
     <t>unique count of (Request Status)-RTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABM Terr Code </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,7 +317,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -374,12 +366,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -573,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -673,9 +659,6 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -736,26 +719,23 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1092,67 +1072,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9760C12-457D-4B77-BE71-2AFD5C035BB8}">
   <dimension ref="B1:T8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="11.1796875" customWidth="1"/>
-    <col min="14" max="14" width="11.1796875" style="2" customWidth="1"/>
-    <col min="15" max="19" width="11.1796875" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="11.19921875" customWidth="1"/>
+    <col min="14" max="14" width="11.19921875" style="2" customWidth="1"/>
+    <col min="15" max="19" width="11.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:20" ht="14.4" thickBot="1">
       <c r="B1" t="s">
         <v>43</v>
       </c>
       <c r="N1"/>
     </row>
-    <row r="2" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="47" t="s">
+    <row r="2" spans="2:20" ht="15" customHeight="1">
+      <c r="B2" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="49" t="s">
+      <c r="D2" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="56"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="38" t="s">
+      <c r="H2" s="55"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="39"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="41" t="s">
+      <c r="K2" s="38"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="42"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="44" t="s">
+      <c r="N2" s="41"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="46"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="45"/>
       <c r="T2" s="1"/>
     </row>
-    <row r="3" spans="2:20" ht="52" x14ac:dyDescent="0.35">
-      <c r="B3" s="48"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="54"/>
+    <row r="3" spans="2:20" ht="55.2">
+      <c r="B3" s="47"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="53"/>
       <c r="G3" s="24" t="s">
         <v>13</v>
       </c>
@@ -1193,7 +1173,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:20">
       <c r="B4" s="17" t="s">
         <v>37</v>
       </c>
@@ -1248,7 +1228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:20">
       <c r="B5" s="17" t="s">
         <v>38</v>
       </c>
@@ -1296,7 +1276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:20">
       <c r="B6" s="17" t="s">
         <v>39</v>
       </c>
@@ -1344,7 +1324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:20">
       <c r="B7" s="17" t="s">
         <v>40</v>
       </c>
@@ -1392,7 +1372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:20" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:20" s="1" customFormat="1" ht="14.4" thickBot="1">
       <c r="B8" s="19"/>
       <c r="C8" s="20" t="s">
         <v>6</v>
@@ -1477,240 +1457,270 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DACB1CB7-14A2-4E13-A57E-9A753E37F862}">
-  <dimension ref="B1:S9"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:S8"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" style="10" customWidth="1"/>
     <col min="2" max="2" width="17" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="10"/>
-    <col min="5" max="5" width="12.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.90625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" style="10" customWidth="1"/>
-    <col min="8" max="13" width="13.90625" style="10" customWidth="1"/>
-    <col min="14" max="14" width="13.90625" style="14" customWidth="1"/>
-    <col min="15" max="19" width="13.90625" style="10" customWidth="1"/>
-    <col min="20" max="16384" width="8.7265625" style="10"/>
+    <col min="3" max="3" width="18.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69921875" style="10"/>
+    <col min="5" max="5" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.8984375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="15.3984375" style="10" customWidth="1"/>
+    <col min="8" max="13" width="13.8984375" style="10" customWidth="1"/>
+    <col min="14" max="14" width="13.8984375" style="14" customWidth="1"/>
+    <col min="15" max="19" width="13.8984375" style="10" customWidth="1"/>
+    <col min="20" max="16384" width="8.69921875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="186" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:19" ht="171.6">
       <c r="B1" s="36" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="36" t="s">
         <v>44</v>
       </c>
       <c r="E1" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="J1" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="K1" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="J1" s="36" t="s">
+      <c r="O1" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="L1" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="M1" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="N1" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="O1" s="36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="2:19" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="C2" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="64" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="N2" s="10"/>
-    </row>
-    <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="59" t="s">
+    </row>
+    <row r="2" spans="2:19" ht="15" customHeight="1">
+      <c r="B2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C2" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D2" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E2" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="58" t="s">
+      <c r="F2" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="60" t="s">
+      <c r="G2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61" t="s">
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="61"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="62" t="s">
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63" t="s">
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-    </row>
-    <row r="4" spans="2:19" ht="39" x14ac:dyDescent="0.3">
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="6" t="s">
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+    </row>
+    <row r="3" spans="2:19" ht="41.4">
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="11" t="s">
+      <c r="R3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="S3" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:19">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="12">
+        <v>12</v>
+      </c>
+      <c r="F4" s="12">
+        <v>13</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12">
+        <v>1</v>
+      </c>
+      <c r="I4" s="15">
+        <f>F4-G4-H4</f>
+        <v>12</v>
+      </c>
+      <c r="J4" s="12">
+        <v>2</v>
+      </c>
+      <c r="K4" s="12">
+        <v>1</v>
+      </c>
+      <c r="L4" s="12">
+        <v>10</v>
+      </c>
+      <c r="M4" s="12">
+        <v>9</v>
+      </c>
+      <c r="N4" s="12">
+        <v>1</v>
+      </c>
+      <c r="O4" s="12">
+        <v>0</v>
+      </c>
+      <c r="P4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <v>0</v>
+      </c>
+      <c r="S4" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19">
       <c r="B5" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" s="12">
+        <v>15</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12">
+        <v>2</v>
+      </c>
+      <c r="I5" s="15"/>
+      <c r="J5" s="12">
+        <v>0</v>
+      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12">
         <v>13</v>
       </c>
-      <c r="G5" s="12">
-        <v>0</v>
-      </c>
-      <c r="H5" s="12">
-        <v>1</v>
-      </c>
-      <c r="I5" s="15">
-        <f>F5-G5-H5</f>
-        <v>12</v>
-      </c>
-      <c r="J5" s="12">
+      <c r="M5" s="12">
+        <v>11</v>
+      </c>
+      <c r="N5" s="12">
+        <v>1</v>
+      </c>
+      <c r="O5" s="12">
+        <v>1</v>
+      </c>
+      <c r="P5" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>1</v>
+      </c>
+      <c r="R5" s="12">
+        <v>0</v>
+      </c>
+      <c r="S5" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19">
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="K5" s="12">
-        <v>1</v>
-      </c>
-      <c r="L5" s="12">
-        <v>10</v>
-      </c>
-      <c r="M5" s="12">
-        <v>9</v>
-      </c>
-      <c r="N5" s="12">
-        <v>1</v>
-      </c>
-      <c r="O5" s="12">
-        <v>0</v>
-      </c>
-      <c r="P5" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>0</v>
-      </c>
-      <c r="R5" s="12">
-        <v>0</v>
-      </c>
-      <c r="S5" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>1</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="12">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="F6" s="12">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="12">
@@ -1718,22 +1728,22 @@
       </c>
       <c r="K6" s="12"/>
       <c r="L6" s="12">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="M6" s="12">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="N6" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="12">
         <v>0</v>
       </c>
       <c r="Q6" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="12">
         <v>0</v>
@@ -1742,23 +1752,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:19">
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="12">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="F7" s="12">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="12">
@@ -1766,224 +1776,177 @@
       </c>
       <c r="K7" s="12"/>
       <c r="L7" s="12">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="M7" s="12">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="N7" s="12">
         <v>0</v>
       </c>
       <c r="O7" s="12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P7" s="12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q7" s="12">
         <v>0</v>
       </c>
       <c r="R7" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S7" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="2:19" s="13" customFormat="1">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="16">
+        <f>SUM(E4:E7)</f>
+        <v>113</v>
+      </c>
+      <c r="F8" s="16">
+        <f t="shared" ref="F8:S8" si="0">SUM(F4:F7)</f>
+        <v>133</v>
+      </c>
+      <c r="G8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="16">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="12">
+      <c r="I8" s="16">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="F8" s="12">
-        <v>25</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12">
-        <v>4</v>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="12">
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12">
-        <v>21</v>
-      </c>
-      <c r="M8" s="12">
-        <v>13</v>
-      </c>
-      <c r="N8" s="12">
-        <v>0</v>
-      </c>
-      <c r="O8" s="12">
-        <v>8</v>
-      </c>
-      <c r="P8" s="12">
+      <c r="J8" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K8" s="16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L8" s="16">
+        <f t="shared" si="0"/>
+        <v>121</v>
+      </c>
+      <c r="M8" s="16">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="N8" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O8" s="16">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="P8" s="16">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="Q8" s="12">
-        <v>0</v>
-      </c>
-      <c r="R8" s="12">
+      <c r="Q8" s="16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R8" s="16">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="S8" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="5"/>
-      <c r="C9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="16">
-        <f>SUM(E5:E8)</f>
-        <v>113</v>
-      </c>
-      <c r="F9" s="16">
-        <f t="shared" ref="F9:S9" si="0">SUM(F5:F8)</f>
-        <v>133</v>
-      </c>
-      <c r="G9" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="16">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="I9" s="16">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="J9" s="16">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K9" s="16">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L9" s="16">
-        <f t="shared" si="0"/>
-        <v>121</v>
-      </c>
-      <c r="M9" s="16">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-      <c r="N9" s="16">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="O9" s="16">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="P9" s="16">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="Q9" s="16">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="R9" s="16">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="S9" s="16">
+      <c r="S8" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5345E43-6F29-4205-A85E-B8E01B76C185}">
   <dimension ref="B1:S8"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="16.6328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.7265625" style="10"/>
-    <col min="6" max="13" width="12.90625" style="10" customWidth="1"/>
-    <col min="14" max="14" width="12.90625" style="14" customWidth="1"/>
-    <col min="15" max="19" width="12.90625" style="10" customWidth="1"/>
-    <col min="20" max="16384" width="8.7265625" style="10"/>
+    <col min="1" max="1" width="2.796875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="16.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.69921875" style="10"/>
+    <col min="6" max="13" width="12.8984375" style="10" customWidth="1"/>
+    <col min="14" max="14" width="12.8984375" style="14" customWidth="1"/>
+    <col min="15" max="19" width="12.8984375" style="10" customWidth="1"/>
+    <col min="20" max="16384" width="8.69921875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:19">
       <c r="N1" s="10"/>
     </row>
-    <row r="2" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="59" t="s">
+    <row r="2" spans="2:19" ht="15" customHeight="1">
+      <c r="B2" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61" t="s">
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="62" t="s">
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="63" t="s">
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="63"/>
-    </row>
-    <row r="3" spans="2:19" ht="39" x14ac:dyDescent="0.3">
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="58"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+    </row>
+    <row r="3" spans="2:19" ht="41.4">
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="61"/>
       <c r="G3" s="6" t="s">
         <v>13</v>
       </c>
@@ -2024,7 +1987,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:19">
       <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
@@ -2079,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:19">
       <c r="B5" s="3" t="s">
         <v>32</v>
       </c>
@@ -2127,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:19">
       <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
@@ -2175,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:19">
       <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
@@ -2223,7 +2186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:19" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:19" s="13" customFormat="1">
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
         <v>6</v>
